--- a/excel_routes/route_HBE_JED_threats.xlsx
+++ b/excel_routes/route_HBE_JED_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +92,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -523,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -533,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>Air Arabia Egypt E5-323</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7286</v>
+        <v>11033</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9729</v>
+        <v>16177</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-2443</v>
+        <v>-5144</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -568,40 +586,40 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SM-451</t>
+          <t>SM-973</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-645</t>
+          <t>Air Arabia Egypt E5-325</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7286</v>
+        <v>8986</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>9729</v>
+        <v>23659</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-2443</v>
+        <v>-14673</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>30</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -613,40 +631,40 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-451</t>
+          <t>SM-973</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7286</v>
+        <v>10048</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9729</v>
+        <v>23659</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-2443</v>
+        <v>-13611</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -658,40 +676,40 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-451</t>
+          <t>SM-973</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-325</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10841</v>
+        <v>10048</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>9729</v>
+        <v>23659</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1112</v>
+        <v>-13611</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -703,40 +721,40 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SM-451</t>
+          <t>SM-973</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7286</v>
+        <v>11863</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>7741</v>
+        <v>23659</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-455</v>
+        <v>-11796</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -748,40 +766,40 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SM-451</t>
+          <t>SM-973</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>Air Arabia Egypt E5-321</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7286</v>
+        <v>14362</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>7741</v>
+        <v>23659</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-455</v>
+        <v>-9297</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>30</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -793,40 +811,40 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>21-JUN-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SM-451</t>
+          <t>SM-973</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>Saudia SV-332</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4954</v>
+        <v>15795</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>7741</v>
+        <v>23659</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-2787</v>
+        <v>-7864</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -838,40 +856,40 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>21-JUN-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SM-451</t>
+          <t>SM-973</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>Saudia SV-410</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7286</v>
+        <v>15795</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>7741</v>
+        <v>23659</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-455</v>
+        <v>-7864</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -883,40 +901,40 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>21-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SM-451</t>
+          <t>SM-989</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7286</v>
+        <v>10048</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7741</v>
+        <v>23659</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-455</v>
+        <v>-13611</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -928,27 +946,27 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SM-451</t>
+          <t>SM-989</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-327</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4954</v>
+        <v>10048</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7741</v>
+        <v>23659</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-2787</v>
+        <v>-13611</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -959,9 +977,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -973,40 +991,40 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SM-451</t>
+          <t>SM-989</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>Air Arabia Egypt E5-323</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4954</v>
+        <v>11033</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>7741</v>
+        <v>23659</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-2787</v>
+        <v>-12626</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>30</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1018,40 +1036,40 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SM-451</t>
+          <t>SM-989</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-669</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7286</v>
+        <v>11863</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>7741</v>
+        <v>23659</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-455</v>
+        <v>-11796</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1063,40 +1081,40 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SM-451</t>
+          <t>SM-989</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>Saudia SV-410</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>4954</v>
+        <v>15795</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>7741</v>
+        <v>23659</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-2787</v>
+        <v>-7864</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1108,27 +1126,27 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SM-451</t>
+          <t>SM-457</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>EgyptAir MS-671</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>8294</v>
+        <v>10553</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>7038</v>
+        <v>11181</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1256</v>
+        <v>-628</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1153,27 +1171,27 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SM-451</t>
+          <t>SM-457</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>EgyptAir MS-661</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>8294</v>
+        <v>10553</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>6348</v>
+        <v>11181</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1946</v>
+        <v>-628</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1198,27 +1216,27 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SM-451</t>
+          <t>SM-457</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>EgyptAir MS-669</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8294</v>
+        <v>10553</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>6348</v>
+        <v>11181</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1946</v>
+        <v>-628</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>46</v>
@@ -1235,366 +1253,6 @@
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>20-JUL-26</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>8294</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>6348</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>1946</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>8294</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>7038</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>1256</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>01-AUG-26</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>10916</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>11219</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-303</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>03-AUG-26</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>10916</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>9729</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>1187</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>05-AUG-26</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>10916</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>9729</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>1187</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>08-AUG-26</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>10916</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>11219</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-303</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>10-AUG-26</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>10916</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>9729</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>1187</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>12-AUG-26</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>11868</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>11219</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>649</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HBE_JED_threats.xlsx
+++ b/excel_routes/route_HBE_JED_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C69B4916-E24A-462C-84E2-67DC119E1233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360C15EB-E628-4800-A731-D1596974C10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -60,67 +60,64 @@
     <t>Currency</t>
   </si>
   <si>
-    <t>02-AUG-26</t>
+    <t>28-JUL-26</t>
+  </si>
+  <si>
+    <t>SM-981</t>
+  </si>
+  <si>
+    <t>Air Arabia Egypt E5-325</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>EGP</t>
+  </si>
+  <si>
+    <t>03-AUG-26</t>
   </si>
   <si>
     <t>SM-451</t>
   </si>
   <si>
-    <t>flyadeal F3-754</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>EGP</t>
+    <t>flyadeal F3-764</t>
+  </si>
+  <si>
+    <t>04-AUG-26</t>
+  </si>
+  <si>
+    <t>SM-973</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>Saudia SV-410</t>
   </si>
   <si>
     <t>Air Arabia Egypt E5-321</t>
   </si>
   <si>
-    <t>Air Arabia Egypt E5-325</t>
-  </si>
-  <si>
-    <t>03-AUG-26</t>
-  </si>
-  <si>
-    <t>flyadeal F3-764</t>
-  </si>
-  <si>
-    <t>04-AUG-26</t>
-  </si>
-  <si>
-    <t>SM-973</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-170</t>
-  </si>
-  <si>
-    <t>flyadeal F3-756</t>
-  </si>
-  <si>
-    <t>flyadeal F3-762</t>
-  </si>
-  <si>
-    <t>Saudia SV-410</t>
-  </si>
-  <si>
     <t>Saudia SV-332</t>
   </si>
   <si>
+    <t>MED</t>
+  </si>
+  <si>
     <t>05-AUG-26</t>
   </si>
   <si>
     <t>SM-989</t>
   </si>
   <si>
+    <t>Air Arabia Egypt E5-323</t>
+  </si>
+  <si>
+    <t>Nile Air NP-227</t>
+  </si>
+  <si>
     <t>Nile Air NP-127</t>
-  </si>
-  <si>
-    <t>Air Arabia Egypt E5-323</t>
   </si>
   <si>
     <t>06-AUG-26</t>
@@ -153,7 +150,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -176,6 +173,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF8D7DA"/>
         <bgColor rgb="FFF8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3CD"/>
+        <bgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -206,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -218,6 +221,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -523,7 +529,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -584,22 +590,22 @@
         <v>13</v>
       </c>
       <c r="D2" s="2">
-        <v>11863</v>
+        <v>17491</v>
       </c>
       <c r="E2" s="2">
-        <v>14676</v>
+        <v>23658</v>
       </c>
       <c r="F2" s="2">
-        <v>-2813</v>
+        <v>-6167</v>
       </c>
       <c r="G2" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H2" s="2">
         <v>30</v>
       </c>
       <c r="I2" s="2">
-        <v>-10</v>
+        <v>30</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>14</v>
@@ -610,22 +616,22 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" s="2">
-        <v>13758</v>
+        <v>11863</v>
       </c>
       <c r="E3" s="2">
-        <v>14676</v>
+        <v>13187</v>
       </c>
       <c r="F3" s="2">
-        <v>-918</v>
+        <v>-1324</v>
       </c>
       <c r="G3" s="2">
         <v>40</v>
@@ -645,34 +651,34 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2">
-        <v>16131</v>
+        <v>9463</v>
       </c>
       <c r="E4" s="2">
-        <v>14676</v>
+        <v>23658</v>
       </c>
       <c r="F4" s="2">
-        <v>1455</v>
+        <v>-14195</v>
       </c>
       <c r="G4" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H4" s="2">
         <v>30</v>
       </c>
       <c r="I4" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>15</v>
@@ -680,34 +686,34 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D5" s="2">
-        <v>11863</v>
+        <v>15795</v>
       </c>
       <c r="E5" s="2">
-        <v>13188</v>
+        <v>23658</v>
       </c>
       <c r="F5" s="2">
-        <v>-1325</v>
+        <v>-7863</v>
       </c>
       <c r="G5" s="2">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H5" s="2">
         <v>30</v>
       </c>
       <c r="I5" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>15</v>
@@ -715,22 +721,22 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2">
-        <v>9507</v>
+        <v>16568</v>
       </c>
       <c r="E6" s="2">
-        <v>23659</v>
+        <v>23658</v>
       </c>
       <c r="F6" s="2">
-        <v>-14152</v>
+        <v>-7090</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
@@ -741,8 +747,8 @@
       <c r="I6" s="2">
         <v>30</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>22</v>
+      <c r="J6" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>15</v>
@@ -750,34 +756,34 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="C7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="2">
+        <v>17174</v>
+      </c>
+      <c r="E7" s="2">
+        <v>23658</v>
+      </c>
+      <c r="F7" s="2">
+        <v>-6484</v>
+      </c>
+      <c r="G7" s="2">
         <v>23</v>
       </c>
-      <c r="D7" s="2">
-        <v>10867</v>
-      </c>
-      <c r="E7" s="2">
-        <v>23659</v>
-      </c>
-      <c r="F7" s="2">
-        <v>-12792</v>
-      </c>
-      <c r="G7" s="2">
-        <v>30</v>
-      </c>
       <c r="H7" s="2">
         <v>30</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>22</v>
+        <v>7</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>15</v>
@@ -785,34 +791,34 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="2">
+        <v>10993</v>
+      </c>
+      <c r="E8" s="2">
+        <v>23658</v>
+      </c>
+      <c r="F8" s="2">
+        <v>-12665</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2">
+        <v>30</v>
+      </c>
+      <c r="J8" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="2">
-        <v>11863</v>
-      </c>
-      <c r="E8" s="2">
-        <v>23659</v>
-      </c>
-      <c r="F8" s="2">
-        <v>-11796</v>
-      </c>
-      <c r="G8" s="2">
-        <v>40</v>
-      </c>
-      <c r="H8" s="2">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>15</v>
@@ -820,34 +826,34 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="2">
+        <v>11181</v>
+      </c>
+      <c r="E9" s="2">
+        <v>23658</v>
+      </c>
+      <c r="F9" s="2">
+        <v>-12477</v>
+      </c>
+      <c r="G9" s="2">
+        <v>15</v>
+      </c>
+      <c r="H9" s="2">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2">
+        <v>15</v>
+      </c>
+      <c r="J9" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="2">
-        <v>12136</v>
-      </c>
-      <c r="E9" s="2">
-        <v>23659</v>
-      </c>
-      <c r="F9" s="2">
-        <v>-11523</v>
-      </c>
-      <c r="G9" s="2">
-        <v>40</v>
-      </c>
-      <c r="H9" s="2">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>15</v>
@@ -855,34 +861,34 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="2">
+        <v>12327</v>
+      </c>
+      <c r="E10" s="2">
+        <v>23658</v>
+      </c>
+      <c r="F10" s="2">
+        <v>-11331</v>
+      </c>
+      <c r="G10" s="2">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="2">
-        <v>15795</v>
-      </c>
-      <c r="E10" s="2">
-        <v>23659</v>
-      </c>
-      <c r="F10" s="2">
-        <v>-7864</v>
-      </c>
-      <c r="G10" s="2">
-        <v>23</v>
-      </c>
-      <c r="H10" s="2">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2">
-        <v>7</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>15</v>
@@ -890,34 +896,34 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="2">
+        <v>12327</v>
+      </c>
+      <c r="E11" s="2">
+        <v>23658</v>
+      </c>
+      <c r="F11" s="2">
+        <v>-11331</v>
+      </c>
+      <c r="G11" s="2">
+        <v>30</v>
+      </c>
+      <c r="H11" s="2">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="2">
-        <v>16645</v>
-      </c>
-      <c r="E11" s="2">
-        <v>23659</v>
-      </c>
-      <c r="F11" s="2">
-        <v>-7014</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2">
-        <v>30</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>15</v>
@@ -925,34 +931,34 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="2">
+        <v>15795</v>
+      </c>
+      <c r="E12" s="2">
+        <v>23658</v>
+      </c>
+      <c r="F12" s="2">
+        <v>-7863</v>
+      </c>
+      <c r="G12" s="2">
+        <v>23</v>
+      </c>
+      <c r="H12" s="2">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7</v>
+      </c>
+      <c r="J12" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="2">
-        <v>17761</v>
-      </c>
-      <c r="E12" s="2">
-        <v>23659</v>
-      </c>
-      <c r="F12" s="2">
-        <v>-5898</v>
-      </c>
-      <c r="G12" s="2">
-        <v>46</v>
-      </c>
-      <c r="H12" s="2">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>15</v>
@@ -960,211 +966,36 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D13" s="2">
-        <v>10444</v>
+        <v>6471</v>
       </c>
       <c r="E13" s="2">
-        <v>23659</v>
+        <v>11181</v>
       </c>
       <c r="F13" s="2">
-        <v>-13215</v>
+        <v>-4710</v>
       </c>
       <c r="G13" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2">
         <v>30</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="2">
-        <v>11037</v>
-      </c>
-      <c r="E14" s="2">
-        <v>23659</v>
-      </c>
-      <c r="F14" s="2">
-        <v>-12622</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2">
-        <v>30</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="2">
-        <v>11863</v>
-      </c>
-      <c r="E15" s="2">
-        <v>23659</v>
-      </c>
-      <c r="F15" s="2">
-        <v>-11796</v>
-      </c>
-      <c r="G15" s="2">
-        <v>40</v>
-      </c>
-      <c r="H15" s="2">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="2">
-        <v>12136</v>
-      </c>
-      <c r="E16" s="2">
-        <v>23659</v>
-      </c>
-      <c r="F16" s="2">
-        <v>-11523</v>
-      </c>
-      <c r="G16" s="2">
-        <v>40</v>
-      </c>
-      <c r="H16" s="2">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="2">
-        <v>15795</v>
-      </c>
-      <c r="E17" s="2">
-        <v>23659</v>
-      </c>
-      <c r="F17" s="2">
-        <v>-7864</v>
-      </c>
-      <c r="G17" s="2">
-        <v>23</v>
-      </c>
-      <c r="H17" s="2">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2">
-        <v>7</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="2">
-        <v>5447</v>
-      </c>
-      <c r="E18" s="2">
-        <v>11181</v>
-      </c>
-      <c r="F18" s="2">
-        <v>-5734</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2">
-        <v>30</v>
-      </c>
-      <c r="I18" s="2">
-        <v>30</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K18" s="2" t="s">
         <v>15</v>
       </c>
     </row>
